--- a/public/samples/sample_bulk_product_upload.xlsx
+++ b/public/samples/sample_bulk_product_upload.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Product_Bulk_Upload" sheetId="1" r:id="rId1"/>
+    <sheet name="Filters" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -513,7 +514,7 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>MANGO</v>
+        <v/>
       </c>
       <c r="F3" t="str">
         <v>2X5</v>
@@ -613,7 +614,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>FOOTBALL</v>
+        <v/>
       </c>
       <c r="F5" t="str">
         <v>7X10</v>
@@ -654,4 +655,41 @@
     <ignoredError numberStoredAsText="1" sqref="A1:P5"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>BRANDS</v>
+      </c>
+      <c r="B1" t="str">
+        <v>CATEGORIES</v>
+      </c>
+      <c r="C1" t="str">
+        <v>GENDER</v>
+      </c>
+      <c r="D1" t="str">
+        <v>COLOR</v>
+      </c>
+      <c r="E1" t="str">
+        <v>MATERIAL</v>
+      </c>
+      <c r="F1" t="str">
+        <v>UPPER MATERIAL</v>
+      </c>
+      <c r="G1" t="str">
+        <v>PACKING TYPE</v>
+      </c>
+      <c r="H1" t="str">
+        <v>VARIANT</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
+  </ignoredErrors>
+</worksheet>
 </file>